--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.54203219399824</v>
+        <v>10.97558023152471</v>
       </c>
       <c r="D2" t="n">
-        <v>49.88236161209691</v>
+        <v>8.10588376196575</v>
       </c>
       <c r="E2" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F2" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.14869264213212</v>
+        <v>10.26166255434647</v>
       </c>
       <c r="D3" t="n">
-        <v>40.35467754796215</v>
+        <v>6.557635101543849</v>
       </c>
       <c r="E3" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F3" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.637630874054</v>
+        <v>9.691115017033775</v>
       </c>
       <c r="D4" t="n">
-        <v>24.52039967047846</v>
+        <v>3.98456494645275</v>
       </c>
       <c r="E4" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F4" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.57102426245255</v>
+        <v>8.86779144264854</v>
       </c>
       <c r="D5" t="n">
-        <v>21.52324325003088</v>
+        <v>3.497527028130019</v>
       </c>
       <c r="E5" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F5" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.10557839297131</v>
+        <v>10.57965648885784</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58551625985343</v>
+        <v>5.945146392226183</v>
       </c>
       <c r="E6" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F6" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28624460980081</v>
+        <v>3.134014749092631</v>
       </c>
       <c r="D7" t="n">
-        <v>19.36447790009473</v>
+        <v>3.146727658765395</v>
       </c>
       <c r="E7" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F7" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.09291554969965</v>
+        <v>6.515098776826194</v>
       </c>
       <c r="D8" t="n">
-        <v>38.25156904262211</v>
+        <v>6.215879969426092</v>
       </c>
       <c r="E8" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F8" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>55.28959322209984</v>
+        <v>8.984558898591224</v>
       </c>
       <c r="D9" t="n">
-        <v>50.20751335249356</v>
+        <v>8.158720919780203</v>
       </c>
       <c r="E9" t="n">
-        <v>15.06624366115272</v>
+        <v>2.448264594937317</v>
       </c>
       <c r="F9" t="n">
-        <v>11.34882901580807</v>
+        <v>1.844184715068811</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
